--- a/BASE DE DATOS/PreLiquidacion Mercaderista_Supervisor_Lider_Agosto.xlsx
+++ b/BASE DE DATOS/PreLiquidacion Mercaderista_Supervisor_Lider_Agosto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Datos\BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E86460-3D05-45D7-90B6-1FBE9587BF5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E043DEA-947A-407C-A470-5C1CBE45D547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" tabRatio="834" xr2:uid="{63BB9A3D-9F7F-4E36-95B4-EC569DF2BACA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="834" activeTab="3" xr2:uid="{63BB9A3D-9F7F-4E36-95B4-EC569DF2BACA}"/>
   </bookViews>
   <sheets>
     <sheet name="Liquidacion Lideres y Superviso" sheetId="25" r:id="rId1"/>
@@ -29,7 +29,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="2" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -7360,7 +7360,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7FEE3206-7AB6-4DA3-B25C-A774CC63ECEC}" name="TablaDinámica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="COORDINADOR">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7FEE3206-7AB6-4DA3-B25C-A774CC63ECEC}" name="TablaDinámica6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="COORDINADOR">
   <location ref="B44:D48" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="26">
     <pivotField showAll="0"/>
@@ -7487,7 +7487,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{933383BF-2662-4A6D-8C37-D4C117576220}" name="TablaDinámica5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="COORDINADOR">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{933383BF-2662-4A6D-8C37-D4C117576220}" name="TablaDinámica5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="COORDINADOR">
   <location ref="B27:D41" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="26">
     <pivotField showAll="0"/>
@@ -7651,7 +7651,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{08A816D1-E333-4CF8-B21D-2892ED73AF8E}" name="TablaDinámica4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="COORDINADOR">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{08A816D1-E333-4CF8-B21D-2892ED73AF8E}" name="TablaDinámica4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="COORDINADOR">
   <location ref="B20:E24" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="26">
     <pivotField showAll="0"/>
@@ -7782,7 +7782,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4E38805-4325-4BEC-95CE-769A4DA357FE}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="COORDINADOR">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4E38805-4325-4BEC-95CE-769A4DA357FE}" name="TablaDinámica3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="COORDINADOR">
   <location ref="B3:E17" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="26">
     <pivotField showAll="0"/>
@@ -26993,6 +26993,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601843DC-6001-45D3-945D-EDC852DC452B}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AA189"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -27107,7 +27108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="67" t="s">
         <v>353</v>
       </c>
@@ -27188,7 +27189,7 @@
       </c>
       <c r="AA2" s="67"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="67" t="s">
         <v>353</v>
       </c>
@@ -27269,7 +27270,7 @@
       </c>
       <c r="AA3" s="67"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>353</v>
       </c>
@@ -27350,7 +27351,7 @@
       </c>
       <c r="AA4" s="67"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="67" t="s">
         <v>353</v>
       </c>
@@ -27431,7 +27432,7 @@
       </c>
       <c r="AA5" s="67"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="67" t="s">
         <v>353</v>
       </c>
@@ -27512,7 +27513,7 @@
       </c>
       <c r="AA6" s="67"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="67" t="s">
         <v>353</v>
       </c>
@@ -27593,7 +27594,7 @@
       </c>
       <c r="AA7" s="67"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="67" t="s">
         <v>353</v>
       </c>
@@ -27674,7 +27675,7 @@
       </c>
       <c r="AA8" s="67"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
         <v>353</v>
       </c>
@@ -27755,7 +27756,7 @@
       </c>
       <c r="AA9" s="67"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
         <v>353</v>
       </c>
@@ -27836,7 +27837,7 @@
       </c>
       <c r="AA10" s="67"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="67" t="s">
         <v>353</v>
       </c>
@@ -27917,7 +27918,7 @@
       </c>
       <c r="AA11" s="67"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="67" t="s">
         <v>353</v>
       </c>
@@ -27998,7 +27999,7 @@
       </c>
       <c r="AA12" s="67"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="67" t="s">
         <v>353</v>
       </c>
@@ -28079,7 +28080,7 @@
       </c>
       <c r="AA13" s="67"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="67" t="s">
         <v>353</v>
       </c>
@@ -28160,7 +28161,7 @@
       </c>
       <c r="AA14" s="67"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="67" t="s">
         <v>353</v>
       </c>
@@ -28241,7 +28242,7 @@
       </c>
       <c r="AA15" s="67"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="67" t="s">
         <v>353</v>
       </c>
@@ -28322,7 +28323,7 @@
       </c>
       <c r="AA16" s="67"/>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67" t="s">
         <v>353</v>
       </c>
@@ -28403,7 +28404,7 @@
       </c>
       <c r="AA17" s="67"/>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="67" t="s">
         <v>353</v>
       </c>
@@ -28484,7 +28485,7 @@
       </c>
       <c r="AA18" s="67"/>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="67" t="s">
         <v>353</v>
       </c>
@@ -28565,7 +28566,7 @@
       </c>
       <c r="AA19" s="67"/>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="67" t="s">
         <v>353</v>
       </c>
@@ -28646,7 +28647,7 @@
       </c>
       <c r="AA20" s="67"/>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="67" t="s">
         <v>353</v>
       </c>
@@ -28727,7 +28728,7 @@
       </c>
       <c r="AA21" s="67"/>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="67" t="s">
         <v>353</v>
       </c>
@@ -28808,7 +28809,7 @@
       </c>
       <c r="AA22" s="67"/>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="67" t="s">
         <v>353</v>
       </c>
@@ -28889,7 +28890,7 @@
       </c>
       <c r="AA23" s="67"/>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="67" t="s">
         <v>353</v>
       </c>
@@ -28970,7 +28971,7 @@
       </c>
       <c r="AA24" s="67"/>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="67" t="s">
         <v>353</v>
       </c>
@@ -29051,7 +29052,7 @@
       </c>
       <c r="AA25" s="67"/>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="67" t="s">
         <v>353</v>
       </c>
@@ -29132,7 +29133,7 @@
       </c>
       <c r="AA26" s="67"/>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="67" t="s">
         <v>353</v>
       </c>
@@ -29294,7 +29295,7 @@
       </c>
       <c r="AA28" s="67"/>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="67" t="s">
         <v>353</v>
       </c>
@@ -29375,7 +29376,7 @@
       </c>
       <c r="AA29" s="67"/>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="67" t="s">
         <v>353</v>
       </c>
@@ -29456,7 +29457,7 @@
       </c>
       <c r="AA30" s="67"/>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="67" t="s">
         <v>353</v>
       </c>
@@ -29537,7 +29538,7 @@
       </c>
       <c r="AA31" s="67"/>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="67" t="s">
         <v>353</v>
       </c>
@@ -29618,7 +29619,7 @@
       </c>
       <c r="AA32" s="67"/>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="67" t="s">
         <v>353</v>
       </c>
@@ -29699,7 +29700,7 @@
       </c>
       <c r="AA33" s="67"/>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="67" t="s">
         <v>353</v>
       </c>
@@ -29780,7 +29781,7 @@
       </c>
       <c r="AA34" s="67"/>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="67" t="s">
         <v>353</v>
       </c>
@@ -29861,7 +29862,7 @@
       </c>
       <c r="AA35" s="67"/>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="67" t="s">
         <v>353</v>
       </c>
@@ -29942,7 +29943,7 @@
       </c>
       <c r="AA36" s="67"/>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="67" t="s">
         <v>353</v>
       </c>
@@ -30023,7 +30024,7 @@
       </c>
       <c r="AA37" s="67"/>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="67" t="s">
         <v>353</v>
       </c>
@@ -30104,7 +30105,7 @@
       </c>
       <c r="AA38" s="67"/>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="67" t="s">
         <v>353</v>
       </c>
@@ -30185,7 +30186,7 @@
       </c>
       <c r="AA39" s="67"/>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="67" t="s">
         <v>353</v>
       </c>
@@ -30266,7 +30267,7 @@
       </c>
       <c r="AA40" s="67"/>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="67" t="s">
         <v>353</v>
       </c>
@@ -30347,7 +30348,7 @@
       </c>
       <c r="AA41" s="67"/>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="67" t="s">
         <v>353</v>
       </c>
@@ -30428,7 +30429,7 @@
       </c>
       <c r="AA42" s="67"/>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="67" t="s">
         <v>353</v>
       </c>
@@ -30509,7 +30510,7 @@
       </c>
       <c r="AA43" s="67"/>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="67" t="s">
         <v>353</v>
       </c>
@@ -30590,7 +30591,7 @@
       </c>
       <c r="AA44" s="67"/>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="67" t="s">
         <v>353</v>
       </c>
@@ -30671,7 +30672,7 @@
       </c>
       <c r="AA45" s="67"/>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="67" t="s">
         <v>353</v>
       </c>
@@ -30752,7 +30753,7 @@
       </c>
       <c r="AA46" s="67"/>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="67" t="s">
         <v>353</v>
       </c>
@@ -30833,7 +30834,7 @@
       </c>
       <c r="AA47" s="67"/>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="67" t="s">
         <v>353</v>
       </c>
@@ -30914,7 +30915,7 @@
       </c>
       <c r="AA48" s="67"/>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="67" t="s">
         <v>353</v>
       </c>
@@ -30995,7 +30996,7 @@
       </c>
       <c r="AA49" s="67"/>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="67" t="s">
         <v>353</v>
       </c>
@@ -31076,7 +31077,7 @@
       </c>
       <c r="AA50" s="67"/>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="67" t="s">
         <v>353</v>
       </c>
@@ -31157,7 +31158,7 @@
       </c>
       <c r="AA51" s="67"/>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="67" t="s">
         <v>353</v>
       </c>
@@ -31238,7 +31239,7 @@
       </c>
       <c r="AA52" s="67"/>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="67" t="s">
         <v>353</v>
       </c>
@@ -31319,7 +31320,7 @@
       </c>
       <c r="AA53" s="67"/>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="67" t="s">
         <v>353</v>
       </c>
@@ -31400,7 +31401,7 @@
       </c>
       <c r="AA54" s="67"/>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="67" t="s">
         <v>353</v>
       </c>
@@ -31481,7 +31482,7 @@
       </c>
       <c r="AA55" s="67"/>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="67" t="s">
         <v>353</v>
       </c>
@@ -31562,7 +31563,7 @@
       </c>
       <c r="AA56" s="67"/>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="67" t="s">
         <v>353</v>
       </c>
@@ -31643,7 +31644,7 @@
       </c>
       <c r="AA57" s="67"/>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="67" t="s">
         <v>353</v>
       </c>
@@ -31724,7 +31725,7 @@
       </c>
       <c r="AA58" s="67"/>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="67" t="s">
         <v>353</v>
       </c>
@@ -31805,7 +31806,7 @@
       </c>
       <c r="AA59" s="67"/>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="67" t="s">
         <v>353</v>
       </c>
@@ -31886,7 +31887,7 @@
       </c>
       <c r="AA60" s="67"/>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="67" t="s">
         <v>353</v>
       </c>
@@ -31967,7 +31968,7 @@
       </c>
       <c r="AA61" s="67"/>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="67" t="s">
         <v>353</v>
       </c>
@@ -32048,7 +32049,7 @@
       </c>
       <c r="AA62" s="67"/>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="67" t="s">
         <v>353</v>
       </c>
@@ -32129,7 +32130,7 @@
       </c>
       <c r="AA63" s="67"/>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="67" t="s">
         <v>353</v>
       </c>
@@ -32210,7 +32211,7 @@
       </c>
       <c r="AA64" s="67"/>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="67" t="s">
         <v>353</v>
       </c>
@@ -32291,7 +32292,7 @@
       </c>
       <c r="AA65" s="67"/>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="67" t="s">
         <v>353</v>
       </c>
@@ -32372,7 +32373,7 @@
       </c>
       <c r="AA66" s="67"/>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="67" t="s">
         <v>353</v>
       </c>
@@ -32453,7 +32454,7 @@
       </c>
       <c r="AA67" s="67"/>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="67" t="s">
         <v>353</v>
       </c>
@@ -32534,7 +32535,7 @@
       </c>
       <c r="AA68" s="67"/>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="67" t="s">
         <v>353</v>
       </c>
@@ -32615,7 +32616,7 @@
       </c>
       <c r="AA69" s="67"/>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="67" t="s">
         <v>353</v>
       </c>
@@ -32696,7 +32697,7 @@
       </c>
       <c r="AA70" s="67"/>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="67" t="s">
         <v>353</v>
       </c>
@@ -32777,7 +32778,7 @@
       </c>
       <c r="AA71" s="67"/>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="67" t="s">
         <v>353</v>
       </c>
@@ -32858,7 +32859,7 @@
       </c>
       <c r="AA72" s="67"/>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="67" t="s">
         <v>353</v>
       </c>
@@ -32939,7 +32940,7 @@
       </c>
       <c r="AA73" s="67"/>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="67" t="s">
         <v>353</v>
       </c>
@@ -33020,7 +33021,7 @@
       </c>
       <c r="AA74" s="67"/>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="67" t="s">
         <v>353</v>
       </c>
@@ -33101,7 +33102,7 @@
       </c>
       <c r="AA75" s="67"/>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="67" t="s">
         <v>353</v>
       </c>
@@ -33182,7 +33183,7 @@
       </c>
       <c r="AA76" s="67"/>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="67" t="s">
         <v>353</v>
       </c>
@@ -33263,7 +33264,7 @@
       </c>
       <c r="AA77" s="67"/>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="67" t="s">
         <v>353</v>
       </c>
@@ -33344,7 +33345,7 @@
       </c>
       <c r="AA78" s="67"/>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="67" t="s">
         <v>353</v>
       </c>
@@ -33425,7 +33426,7 @@
       </c>
       <c r="AA79" s="67"/>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="67" t="s">
         <v>353</v>
       </c>
@@ -33506,7 +33507,7 @@
       </c>
       <c r="AA80" s="67"/>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="67" t="s">
         <v>353</v>
       </c>
@@ -33587,7 +33588,7 @@
       </c>
       <c r="AA81" s="67"/>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="67" t="s">
         <v>353</v>
       </c>
@@ -33668,7 +33669,7 @@
       </c>
       <c r="AA82" s="67"/>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="67" t="s">
         <v>353</v>
       </c>
@@ -33749,7 +33750,7 @@
       </c>
       <c r="AA83" s="67"/>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="67" t="s">
         <v>353</v>
       </c>
@@ -33830,7 +33831,7 @@
       </c>
       <c r="AA84" s="67"/>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="67" t="s">
         <v>353</v>
       </c>
@@ -33911,7 +33912,7 @@
       </c>
       <c r="AA85" s="67"/>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="67" t="s">
         <v>353</v>
       </c>
@@ -33992,7 +33993,7 @@
       </c>
       <c r="AA86" s="67"/>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="67" t="s">
         <v>353</v>
       </c>
@@ -34073,7 +34074,7 @@
       </c>
       <c r="AA87" s="67"/>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="67" t="s">
         <v>353</v>
       </c>
@@ -34154,7 +34155,7 @@
       </c>
       <c r="AA88" s="67"/>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="67" t="s">
         <v>353</v>
       </c>
@@ -34235,7 +34236,7 @@
       </c>
       <c r="AA89" s="67"/>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="67" t="s">
         <v>353</v>
       </c>
@@ -34316,7 +34317,7 @@
       </c>
       <c r="AA90" s="67"/>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="67" t="s">
         <v>353</v>
       </c>
@@ -34397,7 +34398,7 @@
       </c>
       <c r="AA91" s="67"/>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="67" t="s">
         <v>353</v>
       </c>
@@ -34478,7 +34479,7 @@
       </c>
       <c r="AA92" s="67"/>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="67" t="s">
         <v>353</v>
       </c>
@@ -34559,7 +34560,7 @@
       </c>
       <c r="AA93" s="67"/>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="67" t="s">
         <v>353</v>
       </c>
@@ -34640,7 +34641,7 @@
       </c>
       <c r="AA94" s="67"/>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="67" t="s">
         <v>353</v>
       </c>
@@ -34721,7 +34722,7 @@
       </c>
       <c r="AA95" s="67"/>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="67" t="s">
         <v>353</v>
       </c>
@@ -34802,7 +34803,7 @@
       </c>
       <c r="AA96" s="67"/>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="67" t="s">
         <v>353</v>
       </c>
@@ -34883,7 +34884,7 @@
       </c>
       <c r="AA97" s="67"/>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="67" t="s">
         <v>353</v>
       </c>
@@ -34964,7 +34965,7 @@
       </c>
       <c r="AA98" s="67"/>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="67" t="s">
         <v>353</v>
       </c>
@@ -35045,7 +35046,7 @@
       </c>
       <c r="AA99" s="67"/>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="67" t="s">
         <v>353</v>
       </c>
@@ -35126,7 +35127,7 @@
       </c>
       <c r="AA100" s="67"/>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="67" t="s">
         <v>353</v>
       </c>
@@ -35207,7 +35208,7 @@
       </c>
       <c r="AA101" s="67"/>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="67" t="s">
         <v>353</v>
       </c>
@@ -35288,7 +35289,7 @@
       </c>
       <c r="AA102" s="67"/>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="67" t="s">
         <v>353</v>
       </c>
@@ -35369,7 +35370,7 @@
       </c>
       <c r="AA103" s="67"/>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="67" t="s">
         <v>353</v>
       </c>
@@ -35450,7 +35451,7 @@
       </c>
       <c r="AA104" s="67"/>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="67" t="s">
         <v>353</v>
       </c>
@@ -35531,7 +35532,7 @@
       </c>
       <c r="AA105" s="67"/>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="67" t="s">
         <v>353</v>
       </c>
@@ -35612,7 +35613,7 @@
       </c>
       <c r="AA106" s="67"/>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="67" t="s">
         <v>353</v>
       </c>
@@ -35693,7 +35694,7 @@
       </c>
       <c r="AA107" s="67"/>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="67" t="s">
         <v>353</v>
       </c>
@@ -35774,7 +35775,7 @@
       </c>
       <c r="AA108" s="67"/>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="67" t="s">
         <v>353</v>
       </c>
@@ -35855,7 +35856,7 @@
       </c>
       <c r="AA109" s="67"/>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="67" t="s">
         <v>353</v>
       </c>
@@ -35936,7 +35937,7 @@
       </c>
       <c r="AA110" s="67"/>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="67" t="s">
         <v>353</v>
       </c>
@@ -36017,7 +36018,7 @@
       </c>
       <c r="AA111" s="67"/>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="67" t="s">
         <v>353</v>
       </c>
@@ -36098,7 +36099,7 @@
       </c>
       <c r="AA112" s="67"/>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="67" t="s">
         <v>353</v>
       </c>
@@ -36179,7 +36180,7 @@
       </c>
       <c r="AA113" s="67"/>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="67" t="s">
         <v>353</v>
       </c>
@@ -36260,7 +36261,7 @@
       </c>
       <c r="AA114" s="67"/>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="67" t="s">
         <v>353</v>
       </c>
@@ -36341,7 +36342,7 @@
       </c>
       <c r="AA115" s="67"/>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="67" t="s">
         <v>353</v>
       </c>
@@ -36422,7 +36423,7 @@
       </c>
       <c r="AA116" s="67"/>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="67" t="s">
         <v>353</v>
       </c>
@@ -36503,7 +36504,7 @@
       </c>
       <c r="AA117" s="67"/>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="67" t="s">
         <v>353</v>
       </c>
@@ -36584,7 +36585,7 @@
       </c>
       <c r="AA118" s="67"/>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="67" t="s">
         <v>353</v>
       </c>
@@ -36665,7 +36666,7 @@
       </c>
       <c r="AA119" s="67"/>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="67" t="s">
         <v>353</v>
       </c>
@@ -36746,7 +36747,7 @@
       </c>
       <c r="AA120" s="67"/>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="67" t="s">
         <v>353</v>
       </c>
@@ -36827,7 +36828,7 @@
       </c>
       <c r="AA121" s="67"/>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="67" t="s">
         <v>353</v>
       </c>
@@ -36908,7 +36909,7 @@
       </c>
       <c r="AA122" s="67"/>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="67" t="s">
         <v>353</v>
       </c>
@@ -36989,7 +36990,7 @@
       </c>
       <c r="AA123" s="67"/>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="67" t="s">
         <v>353</v>
       </c>
@@ -37070,7 +37071,7 @@
       </c>
       <c r="AA124" s="67"/>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="67" t="s">
         <v>353</v>
       </c>
@@ -37151,7 +37152,7 @@
       </c>
       <c r="AA125" s="67"/>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="67" t="s">
         <v>353</v>
       </c>
@@ -37232,7 +37233,7 @@
       </c>
       <c r="AA126" s="67"/>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="67" t="s">
         <v>353</v>
       </c>
@@ -37313,7 +37314,7 @@
       </c>
       <c r="AA127" s="67"/>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="67" t="s">
         <v>353</v>
       </c>
@@ -37394,7 +37395,7 @@
       </c>
       <c r="AA128" s="67"/>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="67" t="s">
         <v>353</v>
       </c>
@@ -37475,7 +37476,7 @@
       </c>
       <c r="AA129" s="67"/>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="67" t="s">
         <v>353</v>
       </c>
@@ -37556,7 +37557,7 @@
       </c>
       <c r="AA130" s="67"/>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="67" t="s">
         <v>353</v>
       </c>
@@ -37637,7 +37638,7 @@
       </c>
       <c r="AA131" s="67"/>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="67" t="s">
         <v>353</v>
       </c>
@@ -37718,7 +37719,7 @@
       </c>
       <c r="AA132" s="67"/>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="67" t="s">
         <v>353</v>
       </c>
@@ -37799,7 +37800,7 @@
       </c>
       <c r="AA133" s="67"/>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="67" t="s">
         <v>353</v>
       </c>
@@ -37880,7 +37881,7 @@
       </c>
       <c r="AA134" s="67"/>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="67" t="s">
         <v>353</v>
       </c>
@@ -37961,7 +37962,7 @@
       </c>
       <c r="AA135" s="67"/>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="67" t="s">
         <v>353</v>
       </c>
@@ -38042,7 +38043,7 @@
       </c>
       <c r="AA136" s="67"/>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="67" t="s">
         <v>353</v>
       </c>
@@ -38123,7 +38124,7 @@
       </c>
       <c r="AA137" s="67"/>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="67" t="s">
         <v>353</v>
       </c>
@@ -38204,7 +38205,7 @@
       </c>
       <c r="AA138" s="67"/>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="67" t="s">
         <v>353</v>
       </c>
@@ -38285,7 +38286,7 @@
       </c>
       <c r="AA139" s="67"/>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="67" t="s">
         <v>353</v>
       </c>
@@ -38366,7 +38367,7 @@
       </c>
       <c r="AA140" s="67"/>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="67" t="s">
         <v>353</v>
       </c>
@@ -38447,7 +38448,7 @@
       </c>
       <c r="AA141" s="67"/>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="67" t="s">
         <v>353</v>
       </c>
@@ -38528,7 +38529,7 @@
       </c>
       <c r="AA142" s="67"/>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="67" t="s">
         <v>353</v>
       </c>
@@ -38609,7 +38610,7 @@
       </c>
       <c r="AA143" s="67"/>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="67" t="s">
         <v>353</v>
       </c>
@@ -38690,7 +38691,7 @@
       </c>
       <c r="AA144" s="67"/>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="67" t="s">
         <v>353</v>
       </c>
@@ -38771,7 +38772,7 @@
       </c>
       <c r="AA145" s="67"/>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="67" t="s">
         <v>353</v>
       </c>
@@ -38852,7 +38853,7 @@
       </c>
       <c r="AA146" s="67"/>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="67" t="s">
         <v>353</v>
       </c>
@@ -38933,7 +38934,7 @@
       </c>
       <c r="AA147" s="67"/>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="67" t="s">
         <v>353</v>
       </c>
@@ -39014,7 +39015,7 @@
       </c>
       <c r="AA148" s="67"/>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="67" t="s">
         <v>353</v>
       </c>
@@ -39095,7 +39096,7 @@
       </c>
       <c r="AA149" s="67"/>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="67" t="s">
         <v>353</v>
       </c>
@@ -39176,7 +39177,7 @@
       </c>
       <c r="AA150" s="67"/>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="67" t="s">
         <v>353</v>
       </c>
@@ -39257,7 +39258,7 @@
       </c>
       <c r="AA151" s="67"/>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="67" t="s">
         <v>353</v>
       </c>
@@ -39338,7 +39339,7 @@
       </c>
       <c r="AA152" s="67"/>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="67" t="s">
         <v>353</v>
       </c>
@@ -39419,7 +39420,7 @@
       </c>
       <c r="AA153" s="67"/>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="67" t="s">
         <v>353</v>
       </c>
@@ -39500,7 +39501,7 @@
       </c>
       <c r="AA154" s="67"/>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="67" t="s">
         <v>353</v>
       </c>
@@ -39581,7 +39582,7 @@
       </c>
       <c r="AA155" s="67"/>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="67" t="s">
         <v>353</v>
       </c>
@@ -39662,7 +39663,7 @@
       </c>
       <c r="AA156" s="67"/>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="67" t="s">
         <v>353</v>
       </c>
@@ -39743,7 +39744,7 @@
       </c>
       <c r="AA157" s="67"/>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="67" t="s">
         <v>353</v>
       </c>
@@ -39824,7 +39825,7 @@
       </c>
       <c r="AA158" s="67"/>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="67" t="s">
         <v>353</v>
       </c>
@@ -39905,7 +39906,7 @@
       </c>
       <c r="AA159" s="67"/>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="67" t="s">
         <v>353</v>
       </c>
@@ -39986,7 +39987,7 @@
       </c>
       <c r="AA160" s="67"/>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="67" t="s">
         <v>353</v>
       </c>
@@ -40067,7 +40068,7 @@
       </c>
       <c r="AA161" s="67"/>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="67" t="s">
         <v>353</v>
       </c>
@@ -40148,7 +40149,7 @@
       </c>
       <c r="AA162" s="67"/>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="67" t="s">
         <v>353</v>
       </c>
@@ -40229,7 +40230,7 @@
       </c>
       <c r="AA163" s="67"/>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="67" t="s">
         <v>353</v>
       </c>
@@ -40310,7 +40311,7 @@
       </c>
       <c r="AA164" s="67"/>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="67" t="s">
         <v>353</v>
       </c>
@@ -40391,7 +40392,7 @@
       </c>
       <c r="AA165" s="67"/>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="67" t="s">
         <v>353</v>
       </c>
@@ -40472,7 +40473,7 @@
       </c>
       <c r="AA166" s="67"/>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="67" t="s">
         <v>353</v>
       </c>
@@ -40553,7 +40554,7 @@
       </c>
       <c r="AA167" s="67"/>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="67" t="s">
         <v>353</v>
       </c>
@@ -40634,7 +40635,7 @@
       </c>
       <c r="AA168" s="67"/>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="67" t="s">
         <v>353</v>
       </c>
@@ -40715,7 +40716,7 @@
       </c>
       <c r="AA169" s="67"/>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="67" t="s">
         <v>353</v>
       </c>
@@ -40796,7 +40797,7 @@
       </c>
       <c r="AA170" s="67"/>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="67" t="s">
         <v>353</v>
       </c>
@@ -40877,7 +40878,7 @@
       </c>
       <c r="AA171" s="67"/>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="67" t="s">
         <v>353</v>
       </c>
@@ -40958,7 +40959,7 @@
       </c>
       <c r="AA172" s="67"/>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="67" t="s">
         <v>353</v>
       </c>
@@ -41039,7 +41040,7 @@
       </c>
       <c r="AA173" s="67"/>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="67" t="s">
         <v>353</v>
       </c>
@@ -41120,7 +41121,7 @@
       </c>
       <c r="AA174" s="67"/>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="67" t="s">
         <v>353</v>
       </c>
@@ -41201,7 +41202,7 @@
       </c>
       <c r="AA175" s="67"/>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="67" t="s">
         <v>353</v>
       </c>
@@ -41282,7 +41283,7 @@
       </c>
       <c r="AA176" s="67"/>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="67" t="s">
         <v>353</v>
       </c>
@@ -41363,7 +41364,7 @@
       </c>
       <c r="AA177" s="67"/>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="67" t="s">
         <v>353</v>
       </c>
@@ -41444,7 +41445,7 @@
       </c>
       <c r="AA178" s="67"/>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="67" t="s">
         <v>353</v>
       </c>
@@ -41525,7 +41526,7 @@
       </c>
       <c r="AA179" s="67"/>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="67" t="s">
         <v>353</v>
       </c>
@@ -41606,7 +41607,7 @@
       </c>
       <c r="AA180" s="67"/>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="67" t="s">
         <v>353</v>
       </c>
@@ -41687,7 +41688,7 @@
       </c>
       <c r="AA181" s="67"/>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="67" t="s">
         <v>353</v>
       </c>
@@ -41768,7 +41769,7 @@
       </c>
       <c r="AA182" s="67"/>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="67" t="s">
         <v>353</v>
       </c>
@@ -41849,7 +41850,7 @@
       </c>
       <c r="AA183" s="67"/>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="67" t="s">
         <v>353</v>
       </c>
@@ -41930,7 +41931,7 @@
       </c>
       <c r="AA184" s="67"/>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="67" t="s">
         <v>353</v>
       </c>
@@ -42011,7 +42012,7 @@
       </c>
       <c r="AA185" s="67"/>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="67" t="s">
         <v>353</v>
       </c>
@@ -42092,7 +42093,7 @@
       </c>
       <c r="AA186" s="67"/>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="67" t="s">
         <v>353</v>
       </c>
@@ -42173,7 +42174,7 @@
       </c>
       <c r="AA187" s="67"/>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="67" t="s">
         <v>353</v>
       </c>
@@ -42254,7 +42255,7 @@
       </c>
       <c r="AA188" s="67"/>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="67" t="s">
         <v>353</v>
       </c>
@@ -42336,7 +42337,13 @@
       <c r="AA189" s="67"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA189" xr:uid="{601843DC-6001-45D3-945D-EDC852DC452B}"/>
+  <autoFilter ref="A1:AA189" xr:uid="{601843DC-6001-45D3-945D-EDC852DC452B}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="SOR_4"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
